--- a/docs/SRS/SRS_Template.xlsx
+++ b/docs/SRS/SRS_Template.xlsx
@@ -1,40 +1,90 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vigne\Projects\EV_Battery_QA_Project\docs\SRS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BE6296-7778-4BEB-B803-C9D1862FB468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional_Requirements" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non_Functional_Requirements" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Limitations" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Functional_Requirements" sheetId="1" r:id="rId1"/>
+    <sheet name="Non_Functional_Requirements" sheetId="2" r:id="rId2"/>
+    <sheet name="Assumptions" sheetId="3" r:id="rId3"/>
+    <sheet name="Limitations" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="13">
+  <si>
+    <t>Requirement ID</t>
+  </si>
+  <si>
+    <t>Requirement Description</t>
+  </si>
+  <si>
+    <t>Requirement Type</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Source Requirement ID</t>
+  </si>
+  <si>
+    <t>Verification Method</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Assumption ID</t>
+  </si>
+  <si>
+    <t>Assumption Description</t>
+  </si>
+  <si>
+    <t>Limitation ID</t>
+  </si>
+  <si>
+    <t>Limitation Description</t>
+  </si>
+  <si>
+    <t>ASIL Level</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -53,81 +103,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -415,64 +406,109 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="22.1796875" customWidth="1"/>
+    <col min="8" max="9" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Requirement ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Requirement Description</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Requirement Type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Source Requirement ID</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Verification Method</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{7E58204D-58BB-483D-829A-BA7D4A444BE9}">
+      <formula1>"Functional, Non-Functional, Interface, Safety, Performance, Diagnostic, Testing, Logging, Automation"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{8FA9E9D3-C3C2-4E54-B625-9D6138B5AF7B}">
+      <formula1>"High, Medium, Low, Critical"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{D57D3616-7AAE-464F-AC22-45A030D8E5FA}">
+      <formula1>"Unit Testing Integration Testing System Testing Code Review Analysis Inspection Simulation Demonstration"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576" xr:uid="{19E3264B-707B-484F-A58C-AD948B467AF3}">
+      <formula1>"Draft, Under Review, Approved, Implemented, Tested, Closed, Rejected"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576" xr:uid="{B3B853A0-3368-4C4A-8EAC-58E24873D580}">
+      <formula1>"QM, ASIL-A, ASIL-B, ASIL-C, ASIL-D, NA"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="8" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -480,65 +516,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Requirement ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Requirement Description</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Requirement Type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Source Requirement ID</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Verification Method</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -546,71 +542,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Assumption ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Assumption Description</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Limitation ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Limitation Description</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
